--- a/outputs/57445.xlsx
+++ b/outputs/57445.xlsx
@@ -203,47 +203,47 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -507,7 +507,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="3" width="9.11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -524,7 +524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -538,10 +538,11 @@
         <v>300</v>
       </c>
       <c r="E2" s="2" t="n">
+        <f aca="false">SUMPRODUCT(('Package &amp; Weight Data'!$A$2:$A$10=C2)*('Package &amp; Weight Data'!$B$2:$B$10&lt;=D2)*('Package &amp; Weight Data'!$C$2:$C$10&gt;=D2)*'Package &amp; Weight Data'!$D$2:$D$10)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -555,10 +556,11 @@
         <v>750</v>
       </c>
       <c r="E3" s="2" t="n">
+        <f aca="false">SUMPRODUCT(('Package &amp; Weight Data'!$A$2:$A$10=C3)*('Package &amp; Weight Data'!$B$2:$B$10&lt;=D3)*('Package &amp; Weight Data'!$C$2:$C$10&gt;=D3)*'Package &amp; Weight Data'!$D$2:$D$10)</f>
         <v>2.5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -572,10 +574,11 @@
         <v>2000</v>
       </c>
       <c r="E4" s="2" t="n">
+        <f aca="false">SUMPRODUCT(('Package &amp; Weight Data'!$A$2:$A$10=C4)*('Package &amp; Weight Data'!$B$2:$B$10&lt;=D4)*('Package &amp; Weight Data'!$C$2:$C$10&gt;=D4)*'Package &amp; Weight Data'!$D$2:$D$10)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -589,6 +592,7 @@
         <v>5050</v>
       </c>
       <c r="E5" s="2" t="n">
+        <f aca="false">SUMPRODUCT(('Package &amp; Weight Data'!$A$2:$A$10=C5)*('Package &amp; Weight Data'!$B$2:$B$10&lt;=D5)*('Package &amp; Weight Data'!$C$2:$C$10&gt;=D5)*'Package &amp; Weight Data'!$D$2:$D$10)</f>
         <v>6</v>
       </c>
     </row>
@@ -618,7 +622,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="3" width="9.11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
@@ -632,7 +636,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
@@ -646,7 +650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
@@ -660,7 +664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
@@ -674,7 +678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>10</v>
       </c>
@@ -688,7 +692,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
@@ -702,7 +706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>10</v>
       </c>
@@ -716,7 +720,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
         <v>16</v>
       </c>
@@ -730,7 +734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
         <v>16</v>
       </c>
@@ -744,7 +748,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -758,12 +762,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N18" s="11"/>
       <c r="O18" s="1"/>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="2"/>

--- a/outputs/57445.xlsx
+++ b/outputs/57445.xlsx
@@ -538,7 +538,6 @@
         <v>300</v>
       </c>
       <c r="E2" s="2" t="n">
-        <f aca="false">SUMPRODUCT(('Package &amp; Weight Data'!$A$2:$A$10=C2)*('Package &amp; Weight Data'!$B$2:$B$10&lt;=D2)*('Package &amp; Weight Data'!$C$2:$C$10&gt;=D2)*'Package &amp; Weight Data'!$D$2:$D$10)</f>
         <v>2</v>
       </c>
     </row>
@@ -556,7 +555,6 @@
         <v>750</v>
       </c>
       <c r="E3" s="2" t="n">
-        <f aca="false">SUMPRODUCT(('Package &amp; Weight Data'!$A$2:$A$10=C3)*('Package &amp; Weight Data'!$B$2:$B$10&lt;=D3)*('Package &amp; Weight Data'!$C$2:$C$10&gt;=D3)*'Package &amp; Weight Data'!$D$2:$D$10)</f>
         <v>2.5</v>
       </c>
     </row>
@@ -574,7 +572,6 @@
         <v>2000</v>
       </c>
       <c r="E4" s="2" t="n">
-        <f aca="false">SUMPRODUCT(('Package &amp; Weight Data'!$A$2:$A$10=C4)*('Package &amp; Weight Data'!$B$2:$B$10&lt;=D4)*('Package &amp; Weight Data'!$C$2:$C$10&gt;=D4)*'Package &amp; Weight Data'!$D$2:$D$10)</f>
         <v>18</v>
       </c>
     </row>
@@ -592,7 +589,6 @@
         <v>5050</v>
       </c>
       <c r="E5" s="2" t="n">
-        <f aca="false">SUMPRODUCT(('Package &amp; Weight Data'!$A$2:$A$10=C5)*('Package &amp; Weight Data'!$B$2:$B$10&lt;=D5)*('Package &amp; Weight Data'!$C$2:$C$10&gt;=D5)*'Package &amp; Weight Data'!$D$2:$D$10)</f>
         <v>6</v>
       </c>
     </row>
